--- a/output/pdf_financials_xlsx/MRM.xlsx
+++ b/output/pdf_financials_xlsx/MRM.xlsx
@@ -1094,10 +1094,10 @@
         </is>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.031584</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.125705</v>
       </c>
       <c r="E34" s="3" t="n">
         <v>0</v>
@@ -1136,10 +1136,10 @@
         </is>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.031584</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.125705</v>
       </c>
       <c r="E36" s="3" t="n">
         <v>0</v>
@@ -1388,10 +1388,10 @@
         </is>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.031584</v>
+        <v>0</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.125705</v>
+        <v>0</v>
       </c>
       <c r="E48" s="3" t="n">
         <v>0.273016</v>
@@ -4090,7 +4090,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -6152,7 +6152,7 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E89" s="5" t="n">

--- a/output/pdf_financials_xlsx/MRM.xlsx
+++ b/output/pdf_financials_xlsx/MRM.xlsx
@@ -971,16 +971,16 @@
         </is>
       </c>
       <c r="B28" s="3" t="n">
-        <v>0</v>
+        <v>0.051756</v>
       </c>
       <c r="C28" s="3" t="n">
-        <v>0</v>
+        <v>0.016492</v>
       </c>
       <c r="D28" s="3" t="n">
-        <v>0</v>
+        <v>0.016492</v>
       </c>
       <c r="E28" s="3" t="n">
-        <v>0</v>
+        <v>0.016618</v>
       </c>
     </row>
     <row r="29">
@@ -990,16 +990,16 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-4.57419</v>
+        <v>-4.522434</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-5.38334</v>
+        <v>-5.366848</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-6.125596</v>
+        <v>-6.109104</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-1.337498</v>
+        <v>-1.32088</v>
       </c>
     </row>
     <row r="30">
@@ -2471,16 +2471,16 @@
         </is>
       </c>
       <c r="B100" s="3" t="n">
-        <v>0</v>
+        <v>0.025878</v>
       </c>
       <c r="C100" s="3" t="n">
-        <v>0</v>
+        <v>0.016492</v>
       </c>
       <c r="D100" s="3" t="n">
-        <v>0</v>
+        <v>0.016492</v>
       </c>
       <c r="E100" s="3" t="n">
-        <v>0</v>
+        <v>0.016618</v>
       </c>
     </row>
     <row r="101">
@@ -4198,7 +4198,11 @@
           <t>Depreciation of property and equipment 7</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr"/>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E30" s="5" t="n">
         <v>0.025878</v>
       </c>
@@ -6020,7 +6024,11 @@
           <t>Depreciation of property and equipment 7</t>
         </is>
       </c>
-      <c r="D85" t="inlineStr"/>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E85" s="5" t="n">
         <v>0.025878</v>
       </c>
@@ -9160,7 +9168,11 @@
           <t>Depreciation of property and equipment 7</t>
         </is>
       </c>
-      <c r="D175" t="inlineStr"/>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E175" s="5" t="n">
         <v>0.025878</v>
       </c>

--- a/output/pdf_financials_xlsx/MRM.xlsx
+++ b/output/pdf_financials_xlsx/MRM.xlsx
@@ -2661,16 +2661,16 @@
         </is>
       </c>
       <c r="B110" s="3" t="n">
-        <v>0</v>
+        <v>1.179603</v>
       </c>
       <c r="C110" s="3" t="n">
-        <v>0</v>
+        <v>0.279834</v>
       </c>
       <c r="D110" s="3" t="n">
-        <v>0</v>
+        <v>0.272501</v>
       </c>
       <c r="E110" s="3" t="n">
-        <v>0</v>
+        <v>0.290208</v>
       </c>
     </row>
     <row r="111">
@@ -4232,7 +4232,11 @@
           <t>Accretion expense 11</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr"/>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E31" s="5" t="n">
         <v>1.179603</v>
       </c>
